--- a/app/Console/Commands/noterekapppwp.xlsx
+++ b/app/Console/Commands/noterekapppwp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\simap\app\Console\Commands\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8C1036-4B96-4EBF-8AA2-40528183511B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E40A8FB-4B69-4CE5-AA9F-44C83E6F7DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bangorejo" sheetId="1" r:id="rId1"/>
@@ -21,10 +21,9 @@
     <sheet name="Pesanggaran" sheetId="6" r:id="rId6"/>
     <sheet name="Siliragung" sheetId="7" r:id="rId7"/>
     <sheet name="Singojuruh" sheetId="8" r:id="rId8"/>
-    <sheet name="Songgon" sheetId="9" r:id="rId9"/>
-    <sheet name="Srono" sheetId="10" r:id="rId10"/>
-    <sheet name="Tegalsari" sheetId="11" r:id="rId11"/>
-    <sheet name="Wongsorejo" sheetId="12" r:id="rId12"/>
+    <sheet name="Srono" sheetId="10" r:id="rId9"/>
+    <sheet name="Tegalsari" sheetId="11" r:id="rId10"/>
+    <sheet name="Wongsorejo" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="446">
   <si>
     <t>- Bangorejo / Bangorejo / TPS 001: pengguna hak pilih 223 tidak sama dengan sah+tidak sah 224; pengguna_dpt_pr disesuaikan 118 -&gt; 119.</t>
   </si>
@@ -861,12 +860,6 @@
   </si>
   <si>
     <t>- ... 140 koreksi lainnya tidak ditampilkan.</t>
-  </si>
-  <si>
-    <t>- Songgon / Bedewang / TPS 016: suara sah Excel 227 disesuaikan ke jumlah paslon 217.</t>
-  </si>
-  <si>
-    <t>- Songgon / Bedewang / TPS 016: total suara Excel 227 tidak sama dengan paslon+tidak sah 217; suara tidak sah disesuaikan 0 -&gt; 10.</t>
   </si>
   <si>
     <t>- Srono / Bagorejo / TPS 026: total pengguna Excel 224 tidak sama dengan rincian 225; rincian dipakai.</t>
@@ -1892,513 +1885,233 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B182F6D-BDA6-4E0B-A314-6E8B35429331}">
-  <dimension ref="A1:A101"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A732848E-7EA0-4800-882C-F550CB3D237C}">
+  <dimension ref="A1:A45"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>277</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>278</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>279</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>280</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>281</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>282</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>283</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>284</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>285</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>286</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>287</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>288</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>289</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>290</v>
+        <v>389</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>291</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>292</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>293</v>
+        <v>392</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>294</v>
+        <v>393</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>295</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>296</v>
+        <v>395</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>297</v>
+        <v>396</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>298</v>
+        <v>397</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>299</v>
+        <v>398</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>300</v>
+        <v>399</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>301</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>302</v>
+        <v>401</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>303</v>
+        <v>402</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>304</v>
+        <v>403</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>305</v>
+        <v>404</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>306</v>
+        <v>405</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>307</v>
+        <v>406</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>308</v>
+        <v>407</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>309</v>
+        <v>408</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>310</v>
+        <v>409</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>311</v>
+        <v>410</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>312</v>
+        <v>411</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>313</v>
+        <v>412</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>314</v>
+        <v>413</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>315</v>
+        <v>414</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>316</v>
+        <v>415</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>317</v>
+        <v>416</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>318</v>
+        <v>417</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>319</v>
+        <v>418</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>320</v>
+        <v>419</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A61" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A62" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A63" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A64" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A66" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A67" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A68" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A69" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A70" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A71" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A72" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A73" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A74" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A75" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A76" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A77" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A78" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A79" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A80" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A81" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A82" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A83" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A84" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A85" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A86" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A87" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A88" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A89" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A90" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A91" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A92" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A93" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A94" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A95" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A96" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A97" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A98" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A99" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A100" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A101" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -2407,368 +2120,133 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A732848E-7EA0-4800-882C-F550CB3D237C}">
-  <dimension ref="A1:A45"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>422</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C915792-ABE1-4E81-828C-D09F47E1F370}">
   <dimension ref="A1:A25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -4037,8 +3515,8 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B19A4F9-EAEA-4EA9-B818-B4B87B27986F}">
-  <dimension ref="A1:A2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B182F6D-BDA6-4E0B-A314-6E8B35429331}">
+  <dimension ref="A1:A101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
@@ -4051,6 +3529,501 @@
         <v>276</v>
       </c>
     </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>375</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
